--- a/reports/二级子公司C_利润表_2026-09.xlsx
+++ b/reports/二级子公司C_利润表_2026-09.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>78030225</v>
+        <v>80032487</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>75272400</v>
+        <v>75091918</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>761186480</v>
+        <v>761358180</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>432600</v>
+        <v>432955</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3753320</v>
+        <v>3752364</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>378525</v>
+        <v>379731</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>3284155</v>
+        <v>3284610</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>324450</v>
+        <v>326069</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2814990</v>
+        <v>2816418</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>302820</v>
+        <v>304612</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2627324</v>
+        <v>2629391</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>162225</v>
+        <v>163166</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1407495</v>
+        <v>1408801</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>129780</v>
+        <v>130386</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1125996</v>
+        <v>1127016</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>76299825</v>
+        <v>78295568</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>73542000</v>
+        <v>73354999</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>69216000</v>
+        <v>69063262</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>708640000</v>
+        <v>708851356</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1297800</v>
+        <v>1292218</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>11259960</v>
+        <v>11255964</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>865200</v>
+        <v>860322</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>7506640</v>
+        <v>7501532</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3244500</v>
+        <v>3225086</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>28149900</v>
+        <v>28124958</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>432600</v>
+        <v>430318</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>3753320</v>
+        <v>3749809</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>324450</v>
+        <v>323269</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2814990</v>
+        <v>2812679</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>540750</v>
+        <v>540013</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>4691650</v>
+        <v>4689013</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>648900</v>
+        <v>649648</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>5629980</v>
+        <v>5628833</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2703750</v>
+        <v>2713124</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>23458250</v>
+        <v>23462718</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>54075</v>
+        <v>51766</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>469165</v>
+        <v>463833</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1305540</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>11269131</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>870139</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>7513657</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>69118665</v>
+        <v>73781886</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>62034840</v>
+        <v>62027839</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>60737040</v>
+        <v>60733305</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>502028592</v>
+        <v>502257475</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1297800</v>
+        <v>1294534</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>11259960</v>
+        <v>11259738</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2153203</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>18759034</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>688184</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>6001014</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>430026</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3749933</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>516469</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4499795</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>388030</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3375306</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>259292</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2250825</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>216621</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1876377</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>973350</v>
+        <v>976987</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>8444970</v>
+        <v>8447014</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>757050</v>
+        <v>761088</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>6568310</v>
+        <v>6572205</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>648900</v>
+        <v>652788</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>5629980</v>
+        <v>5634707</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4866750</v>
+        <v>4893981</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>42224850</v>
+        <v>42264480</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>216300</v>
+        <v>217212</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1876660</v>
+        <v>1878297</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>378525</v>
+        <v>361254</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3284155</v>
+        <v>3246347</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>432600</v>
+        <v>361254</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3753320</v>
+        <v>3246347</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>54075</v>
+        <v>51355</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>469165</v>
+        <v>463388</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>184521</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1667563</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>376317</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3281696</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>122871</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1111282</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>92244</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>833514</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>154024</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1389512</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>540372</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4689427</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>82549</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>741645</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>62047</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>556460</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>103564</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>927734</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>72533</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>649535</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>51781</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>463957</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>41363</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>371107</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>30955</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>278246</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>7181160</v>
+        <v>5821937</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>12101985</v>
+        <v>9436226</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>215231</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1875731</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>51196</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>463075</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>86520</v>
+        <v>81920</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>750664</v>
+        <v>740853</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>7094640</v>
+        <v>5955248</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>3028200</v>
+        <v>2875963</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>26273240</v>
+        <v>25938604</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>4066440</v>
+        <v>3079285</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>4066440</v>
+        <v>3079285</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>4066440</v>
+        <v>3079285</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>4066440</v>
+        <v>3079285</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>4066440</v>
+        <v>3079285</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
